--- a/Computer_Science_and_Engineering_Allotment.xlsx
+++ b/Computer_Science_and_Engineering_Allotment.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G29"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -643,19 +643,19 @@
         <v>8</v>
       </c>
       <c r="B11" t="str">
-        <v>Nihal Noushad P</v>
+        <v>MOHAMMED HARIS A</v>
       </c>
       <c r="C11" t="str">
-        <v>796</v>
+        <v>848</v>
       </c>
       <c r="D11" t="str">
         <v>SM</v>
       </c>
       <c r="E11" t="str">
-        <v>nihalnazz0007@gmail.com</v>
+        <v>harisharipcd369@gmail.com</v>
       </c>
       <c r="F11" t="str">
-        <v>8086657850</v>
+        <v>8136903935</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -666,19 +666,19 @@
         <v>9</v>
       </c>
       <c r="B12" t="str">
-        <v>MOHAMMED HARIS A</v>
+        <v>Anandhu Krishnan S</v>
       </c>
       <c r="C12" t="str">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="D12" t="str">
         <v>SM</v>
       </c>
       <c r="E12" t="str">
-        <v>harisharipcd369@gmail.com</v>
+        <v>anandhukrishz07@gmail.com</v>
       </c>
       <c r="F12" t="str">
-        <v>8136903935</v>
+        <v>7994488008</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -689,19 +689,19 @@
         <v>10</v>
       </c>
       <c r="B13" t="str">
-        <v>Anandhu Krishnan S</v>
+        <v>AJAY C</v>
       </c>
       <c r="C13" t="str">
-        <v>855</v>
+        <v>877</v>
       </c>
       <c r="D13" t="str">
         <v>SM</v>
       </c>
       <c r="E13" t="str">
-        <v>anandhukrishz07@gmail.com</v>
+        <v>ajayc9090@gmail.com</v>
       </c>
       <c r="F13" t="str">
-        <v>7994488008</v>
+        <v>8943706586</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -712,19 +712,19 @@
         <v>11</v>
       </c>
       <c r="B14" t="str">
-        <v>AJAY C</v>
+        <v>Shameer A N</v>
       </c>
       <c r="C14" t="str">
-        <v>877</v>
+        <v>931</v>
       </c>
       <c r="D14" t="str">
         <v>SM</v>
       </c>
       <c r="E14" t="str">
-        <v>ajayc9090@gmail.com</v>
+        <v>shameer.an@gmail.com</v>
       </c>
       <c r="F14" t="str">
-        <v>8943706586</v>
+        <v>9895543009</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -735,19 +735,19 @@
         <v>12</v>
       </c>
       <c r="B15" t="str">
-        <v>Shameer A N</v>
+        <v>Shifa thasneem T S</v>
       </c>
       <c r="C15" t="str">
-        <v>931</v>
+        <v>1192</v>
       </c>
       <c r="D15" t="str">
         <v>SM</v>
       </c>
       <c r="E15" t="str">
-        <v>shameer.an@gmail.com</v>
+        <v>shifathasneem96@gmail.com</v>
       </c>
       <c r="F15" t="str">
-        <v>9895543009</v>
+        <v>8606930466</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -758,19 +758,19 @@
         <v>13</v>
       </c>
       <c r="B16" t="str">
-        <v>Shifa thasneem T S</v>
+        <v>APARNA B S</v>
       </c>
       <c r="C16" t="str">
-        <v>1192</v>
+        <v>1555</v>
       </c>
       <c r="D16" t="str">
         <v>SM</v>
       </c>
       <c r="E16" t="str">
-        <v>shifathasneem96@gmail.com</v>
+        <v>shaijuaparna037@gmail.com</v>
       </c>
       <c r="F16" t="str">
-        <v>8606930466</v>
+        <v>9656084511</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>14</v>
       </c>
       <c r="B17" t="str">
-        <v>APARNA B S</v>
+        <v>ANURAGE SS</v>
       </c>
       <c r="C17" t="str">
-        <v>1555</v>
+        <v>1641</v>
       </c>
       <c r="D17" t="str">
         <v>SM</v>
       </c>
       <c r="E17" t="str">
-        <v>shaijuaparna037@gmail.com</v>
+        <v>ssanurage@gmail.com</v>
       </c>
       <c r="F17" t="str">
-        <v>9656084511</v>
+        <v>9778320527</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -804,19 +804,19 @@
         <v>15</v>
       </c>
       <c r="B18" t="str">
-        <v>ANURAGE SS</v>
+        <v>ADITHYAN S R</v>
       </c>
       <c r="C18" t="str">
-        <v>1641</v>
+        <v>1724</v>
       </c>
       <c r="D18" t="str">
         <v>SM</v>
       </c>
       <c r="E18" t="str">
-        <v>ssanurage@gmail.com</v>
+        <v>sr18adithyan@gmail.com</v>
       </c>
       <c r="F18" t="str">
-        <v>9778320527</v>
+        <v>9633309755</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -827,19 +827,19 @@
         <v>16</v>
       </c>
       <c r="B19" t="str">
-        <v>Arunesh M R</v>
+        <v>SHIJINA NIZAR</v>
       </c>
       <c r="C19" t="str">
-        <v>3101</v>
+        <v>1894</v>
       </c>
       <c r="D19" t="str">
-        <v>EZ</v>
+        <v>M</v>
       </c>
       <c r="E19" t="str">
-        <v>aruneshmr@gmail.com</v>
+        <v>shijinanizar14@gmail.com</v>
       </c>
       <c r="F19" t="str">
-        <v>8139889372</v>
+        <v>9747030732</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -850,21 +850,228 @@
         <v>17</v>
       </c>
       <c r="B20" t="str">
+        <v>RAIHANA RAHMAN</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2371</v>
+      </c>
+      <c r="D20" t="str">
+        <v>M</v>
+      </c>
+      <c r="E20" t="str">
+        <v>raihanath.tech@gmail.com</v>
+      </c>
+      <c r="F20" t="str">
+        <v>9778176204</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>18</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SUDHER BP</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2434</v>
+      </c>
+      <c r="D21" t="str">
+        <v>EZ</v>
+      </c>
+      <c r="E21" t="str">
+        <v>sudheerbp341@gmail.com</v>
+      </c>
+      <c r="F21" t="str">
+        <v>8281885113</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>19</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Arif muhammad F</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2734</v>
+      </c>
+      <c r="D22" t="str">
+        <v>M</v>
+      </c>
+      <c r="E22" t="str">
+        <v>arifbussid123@gmail.com</v>
+      </c>
+      <c r="F22" t="str">
+        <v>8943145516</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>20</v>
+      </c>
+      <c r="B23" t="str">
+        <v>SHABANA SN</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2975</v>
+      </c>
+      <c r="D23" t="str">
+        <v>M</v>
+      </c>
+      <c r="E23" t="str">
+        <v>akbarshabana1999@gmail.com</v>
+      </c>
+      <c r="F23" t="str">
+        <v>7034397207</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Rohan Raynish</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2986</v>
+      </c>
+      <c r="D24" t="str">
+        <v>LC</v>
+      </c>
+      <c r="E24" t="str">
+        <v>rohanraynishh@gmail.com</v>
+      </c>
+      <c r="F24" t="str">
+        <v>7907345036</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" t="str">
+        <v>MUNEER M</v>
+      </c>
+      <c r="C25" t="str">
+        <v>3006</v>
+      </c>
+      <c r="D25" t="str">
+        <v>M</v>
+      </c>
+      <c r="E25" t="str">
+        <v>muneer.m@myyahoo.com</v>
+      </c>
+      <c r="F25" t="str">
+        <v>7356630023</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" t="str">
+        <v>ABHISHEK S</v>
+      </c>
+      <c r="C26" t="str">
+        <v>3064</v>
+      </c>
+      <c r="D26" t="str">
+        <v>EWS</v>
+      </c>
+      <c r="E26" t="str">
+        <v>abhishekabhishek4363@gmail.com</v>
+      </c>
+      <c r="F26" t="str">
+        <v>6282597658</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" t="str">
         <v>SARASWATHY T</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C27" t="str">
         <v>3281</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D27" t="str">
         <v>SC</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E27" t="str">
         <v>saraswathykseb@gmail.com</v>
       </c>
-      <c r="F20" t="str">
+      <c r="F27" t="str">
         <v>9446194108</v>
       </c>
-      <c r="G20" t="str">
+      <c r="G27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>25</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Athul Krishnan A S</v>
+      </c>
+      <c r="C28" t="str">
+        <v>3296</v>
+      </c>
+      <c r="D28" t="str">
+        <v>SM</v>
+      </c>
+      <c r="E28" t="str">
+        <v>athulkrishnanas321@gmail.com</v>
+      </c>
+      <c r="F28" t="str">
+        <v>8078114005</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Arunesh M R</v>
+      </c>
+      <c r="C29" t="str">
+        <v>3101</v>
+      </c>
+      <c r="D29" t="str">
+        <v>EZ</v>
+      </c>
+      <c r="E29" t="str">
+        <v>aruneshmr@gmail.com</v>
+      </c>
+      <c r="F29" t="str">
+        <v>8139889372</v>
+      </c>
+      <c r="G29" t="str">
         <v/>
       </c>
     </row>
@@ -874,7 +1081,7 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G29"/>
   </ignoredErrors>
 </worksheet>
 </file>